--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zenitani/Desktop/Meetings/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zenitani/Documents/devel/GeoScience_meetings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B474F38E-FC46-A443-8B65-23F01FE42430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A515E54D-FB5C-BA45-836F-4EA257755E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="500" yWindow="760" windowWidth="28300" windowHeight="16940" xr2:uid="{99737747-559D-0248-BE56-7AD78ED24D49}"/>
   </bookViews>
@@ -1026,8 +1026,14 @@
       <c r="D24" s="4">
         <v>22352</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="7">
         <v>19889</v>
+      </c>
+      <c r="F24" s="7">
+        <v>10321</v>
+      </c>
+      <c r="G24" s="7">
+        <v>8946</v>
       </c>
     </row>
     <row r="26" spans="1:9">

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zenitani/Documents/devel/GeoScience_meetings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A515E54D-FB5C-BA45-836F-4EA257755E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73193E30-3292-364B-84A7-A166C5CC3BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="500" yWindow="760" windowWidth="28300" windowHeight="16940" xr2:uid="{99737747-559D-0248-BE56-7AD78ED24D49}"/>
   </bookViews>
@@ -1035,6 +1035,12 @@
       <c r="G24" s="7">
         <v>8946</v>
       </c>
+      <c r="H24" s="3">
+        <v>3640</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3640</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">

--- a/meetings.xlsx
+++ b/meetings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zenitani/Documents/devel/GeoScience_meetings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73193E30-3292-364B-84A7-A166C5CC3BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D2408D-6007-E446-A2A5-35C2F9EFEA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="500" yWindow="760" windowWidth="28300" windowHeight="16940" xr2:uid="{99737747-559D-0248-BE56-7AD78ED24D49}"/>
   </bookViews>
@@ -984,10 +984,10 @@
         <v>7095</v>
       </c>
       <c r="H22" s="3">
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="I22" s="3">
-        <v>3323</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1013,10 +1013,10 @@
         <v>7903</v>
       </c>
       <c r="H23" s="3">
-        <v>3858</v>
+        <v>3640</v>
       </c>
       <c r="I23" s="3">
-        <v>3858</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1036,10 +1036,10 @@
         <v>8946</v>
       </c>
       <c r="H24" s="3">
-        <v>3640</v>
+        <v>3917</v>
       </c>
       <c r="I24" s="3">
-        <v>3640</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="26" spans="1:9">
